--- a/cviceni/faktury-kontrola/vystup/kontrola-2026-09-08.xlsx
+++ b/cviceni/faktury-kontrola/vystup/kontrola-2026-09-08.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kontrola" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Přehled" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Elektro Dvořák" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,7 +30,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -38,12 +39,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -59,17 +56,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,18 +428,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -457,42 +446,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Číslo faktury</t>
+          <t>Dodavatel</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Dodavatel</t>
+          <t>Kompletní</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>IČO</t>
+          <t>Chybí</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Číslo objednávky</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Částka bez DPH</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Splatnost</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>CHYBÍ</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>SEDÍ</t>
+          <t>E-mail odeslán</t>
         </is>
       </c>
     </row>
@@ -504,38 +473,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FA-2026-0918</t>
+          <t>Stavebniny Morava s.r.o.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Stavebniny Morava s.r.o.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>27182934</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>OBJ-2026-0442</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>48250</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>22. 9. 2026</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
           <t>ano</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -545,159 +492,157 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FA-2026-0919</t>
+          <t>Nářadí Profi a.s.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nářadí Profi a.s.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>45319876</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>OBJ-2026-0447</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>12900</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>25. 9. 2026</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
           <t>ano</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-09-03_elektro-dvorak.pdf</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Elektro Dvořák s.r.o.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>číslo objednávky</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>připraveno, čeká na konektor</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-04_vts-technik.pdf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VTS Technik s.r.o.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-05_barvy-piekarova.pdf</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Barvy Piekarová s.r.o.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Soubor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Číslo faktury</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Chybí</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Navržená odpověď</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>E-mail odeslán</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="90" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03_elektro-dvorak.pdf</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>2026/1044</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Elektro Dvořák s.r.o.</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>61234567</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="5" t="n">
-        <v>7340</v>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>30. 9. 2026</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>číslo objednávky</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>nenalezeno</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-04_vts-technik.pdf</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>FA-2026-0921</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>VTS Technik s.r.o.</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>28374651</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>OBJ-2026-0451</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>33100</v>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>28. 9. 2026</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>ne</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-05_barvy-piekarova.pdf</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>FA-2026-0922</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Barvy Piekarová s.r.o.</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>49876123</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>OBJ-9999-0001</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>5480</v>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>1. 10. 2026</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>nenalezeno</t>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Dobrý den, Elektro Dvořák s.r.o.,
+děkujeme za zaslanou fakturu. Při kontrole naším účetním oddělením jsme nenalezli číslo objednávky, které potřebujeme mít na faktuře. Prosíme o doplnění a opětovné zaslání faktury zpět.
+S pozdravem,
+Účtárna DEK</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>připraveno, čeká na konektor</t>
         </is>
       </c>
     </row>
